--- a/AAII_Financials/Yearly/COOT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/COOT_YR_FIN.xlsx
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>

--- a/AAII_Financials/Yearly/COOT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/COOT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
   <si>
     <t>COOT</t>
   </si>
@@ -662,8 +662,8 @@
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -690,11 +690,11 @@
       <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
+      <c r="G7" s="2">
+        <v>44742</v>
+      </c>
+      <c r="H7" s="2">
+        <v>44377</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>3</v>
@@ -720,11 +720,11 @@
       <c r="F8" s="3">
         <v>19300</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
+      <c r="G8" s="3">
+        <v>17200</v>
+      </c>
+      <c r="H8" s="3">
+        <v>9200</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
@@ -750,11 +750,11 @@
       <c r="F9" s="3">
         <v>16000</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
+      <c r="G9" s="3">
+        <v>13000</v>
+      </c>
+      <c r="H9" s="3">
+        <v>7000</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
@@ -780,11 +780,11 @@
       <c r="F10" s="3">
         <v>3300</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
+      <c r="G10" s="3">
+        <v>4200</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2200</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
@@ -915,10 +915,10 @@
         <v>300</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
@@ -955,11 +955,11 @@
       <c r="F17" s="3">
         <v>17600</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
+      <c r="G17" s="3">
+        <v>15500</v>
+      </c>
+      <c r="H17" s="3">
+        <v>8700</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>3</v>
@@ -985,11 +985,11 @@
       <c r="F18" s="3">
         <v>1700</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
+      <c r="G18" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H18" s="3">
+        <v>600</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
@@ -1029,11 +1029,11 @@
       <c r="F20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
+      <c r="G20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-200</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
@@ -1060,10 +1060,10 @@
         <v>2000</v>
       </c>
       <c r="G21" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H21" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I21" s="3">
         <v>0</v>
@@ -1089,11 +1089,11 @@
       <c r="F22" s="3">
         <v>400</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
+      <c r="G22" s="3">
+        <v>200</v>
+      </c>
+      <c r="H22" s="3">
+        <v>100</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
@@ -1119,11 +1119,11 @@
       <c r="F23" s="3">
         <v>1300</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
+      <c r="G23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H23" s="3">
+        <v>600</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>3</v>
@@ -1209,11 +1209,11 @@
       <c r="F26" s="3">
         <v>1200</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
+      <c r="G26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H26" s="3">
+        <v>600</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>3</v>
@@ -1239,11 +1239,11 @@
       <c r="F27" s="3">
         <v>900</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
+      <c r="G27" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H27" s="3">
+        <v>500</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>3</v>
@@ -1389,11 +1389,11 @@
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
+      <c r="G32" s="3">
+        <v>100</v>
+      </c>
+      <c r="H32" s="3">
+        <v>200</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
@@ -1419,11 +1419,11 @@
       <c r="F33" s="3">
         <v>1000</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
+      <c r="G33" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H33" s="3">
+        <v>500</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>3</v>
@@ -1479,11 +1479,11 @@
       <c r="F35" s="3">
         <v>1000</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
+      <c r="G35" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H35" s="3">
+        <v>500</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>3</v>
@@ -1514,11 +1514,11 @@
       <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
+      <c r="G38" s="2">
+        <v>44742</v>
+      </c>
+      <c r="H38" s="2">
+        <v>44377</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>3</v>
@@ -1572,11 +1572,11 @@
       <c r="F41" s="3">
         <v>100</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
+      <c r="G41" s="3">
+        <v>300</v>
+      </c>
+      <c r="H41" s="3">
+        <v>200</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
@@ -1632,11 +1632,11 @@
       <c r="F43" s="3">
         <v>3000</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
+      <c r="G43" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H43" s="3">
+        <v>600</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
@@ -1662,11 +1662,11 @@
       <c r="F44" s="3">
         <v>3100</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
+      <c r="G44" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H44" s="3">
+        <v>1500</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
@@ -1722,11 +1722,11 @@
       <c r="F46" s="3">
         <v>6500</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
+      <c r="G46" s="3">
+        <v>4500</v>
+      </c>
+      <c r="H46" s="3">
+        <v>2900</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
@@ -1752,11 +1752,11 @@
       <c r="F47" s="3">
         <v>100</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
+      <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
+        <v>0</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
@@ -1782,11 +1782,11 @@
       <c r="F48" s="3">
         <v>7700</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
+      <c r="G48" s="3">
+        <v>5400</v>
+      </c>
+      <c r="H48" s="3">
+        <v>6000</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
@@ -1812,11 +1812,11 @@
       <c r="F49" s="3">
         <v>1700</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
+      <c r="G49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H49" s="3">
+        <v>1900</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
@@ -1962,11 +1962,11 @@
       <c r="F54" s="3">
         <v>16000</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
+      <c r="G54" s="3">
+        <v>11800</v>
+      </c>
+      <c r="H54" s="3">
+        <v>10900</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
@@ -2020,11 +2020,11 @@
       <c r="F57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
+      <c r="G57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H57" s="3">
+        <v>1900</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
@@ -2050,11 +2050,11 @@
       <c r="F58" s="3">
         <v>2400</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
+      <c r="G58" s="3">
+        <v>6900</v>
+      </c>
+      <c r="H58" s="3">
+        <v>4400</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
@@ -2083,8 +2083,8 @@
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
+      <c r="H59" s="3">
+        <v>500</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
@@ -2110,11 +2110,11 @@
       <c r="F60" s="3">
         <v>7000</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
+      <c r="G60" s="3">
+        <v>7400</v>
+      </c>
+      <c r="H60" s="3">
+        <v>6800</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
@@ -2141,10 +2141,10 @@
         <v>3900</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2290,11 +2290,11 @@
       <c r="F66" s="3">
         <v>10900</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
+      <c r="G66" s="3">
+        <v>7500</v>
+      </c>
+      <c r="H66" s="3">
+        <v>7900</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
@@ -2454,11 +2454,11 @@
       <c r="F72" s="3">
         <v>2500</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
+      <c r="G72" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H72" s="3">
+        <v>600</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
@@ -2574,11 +2574,11 @@
       <c r="F76" s="3">
         <v>4200</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
+      <c r="G76" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H76" s="3">
+        <v>2600</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
@@ -2639,11 +2639,11 @@
       <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
+      <c r="G80" s="2">
+        <v>44742</v>
+      </c>
+      <c r="H80" s="2">
+        <v>44377</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>3</v>
@@ -2669,11 +2669,11 @@
       <c r="F81" s="3">
         <v>1000</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
+      <c r="G81" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H81" s="3">
+        <v>500</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>3</v>
@@ -2713,11 +2713,11 @@
       <c r="F83" s="3">
         <v>400</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
+      <c r="G83" s="3">
+        <v>300</v>
+      </c>
+      <c r="H83" s="3">
+        <v>300</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
@@ -2893,11 +2893,11 @@
       <c r="F89" s="3">
         <v>500</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
+      <c r="G89" s="3">
+        <v>400</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-400</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
@@ -2937,11 +2937,11 @@
       <c r="F91" s="3">
         <v>-1900</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
+      <c r="G91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-100</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
@@ -3027,11 +3027,11 @@
       <c r="F94" s="3">
         <v>-1900</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
+      <c r="G94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-100</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
@@ -3191,11 +3191,11 @@
       <c r="F100" s="3">
         <v>1200</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>700</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
@@ -3252,10 +3252,10 @@
         <v>-200</v>
       </c>
       <c r="G102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H102" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I102" s="3">
         <v>0</v>
